--- a/data/availability/projects/mountain-view/mountain-view-icity-new-cairo.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-icity-new-cairo.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for Mountain View iCity New Cairo</t>
+          <t>Live inventory for mountain-view-icity-new-cairo</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,406 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2" t="n">
+        <v>110</v>
+      </c>
+      <c r="F2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="H2" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>205</v>
+      </c>
+      <c r="F3" t="n">
+        <v>205</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="H3" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>520</v>
+      </c>
+      <c r="F4" t="n">
+        <v>565</v>
+      </c>
+      <c r="G4" t="n">
+        <v>83.61</v>
+      </c>
+      <c r="H4" t="n">
+        <v>87.97</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>280</v>
+      </c>
+      <c r="F5" t="n">
+        <v>280</v>
+      </c>
+      <c r="G5" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>300</v>
+      </c>
+      <c r="F6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Phase-3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>260</v>
+      </c>
+      <c r="F7" t="n">
+        <v>260</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="H7" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Feb 2026 (Value Offer)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>255</v>
+      </c>
+      <c r="F8" t="n">
+        <v>255</v>
+      </c>
+      <c r="G8" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="H8" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Phase-1M4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>235</v>
+      </c>
+      <c r="F9" t="n">
+        <v>245</v>
+      </c>
+      <c r="G9" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="H9" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
         </is>
       </c>
     </row>
@@ -557,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +1027,1755 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CA-01-03-BG-1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>140</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Garden: 44.31 sqm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>15682943</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CA-01-03-CG-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>140</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Garden: 75.66 sqm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>17378875</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CA-01-05-BG-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>140</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Garden: 65.15 sqm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>16484278</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CA-01-14-CG-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>140</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Garden: 78.6 sqm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>16650914</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CA-01-15-AG-2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>130</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Garden: 33.86 sqm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>14274110</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CA-01-15-BG-2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>165</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Garden: 87.42 sqm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>19613852</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CA-01-15-BG-5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>110</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Garden: 82.05 sqm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>14472157</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CA-01-16-DG-4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>160</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Garden: 26.6 sqm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>17080848</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CA-01-22-AG-6</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>155</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Garden: 88.76 sqm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>19971995</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CA-01-24-CG-1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>140</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Garden: 35.7 sqm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>15593448</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CA-01-27-CG-1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>140</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Garden: 36.76 sqm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>15593030</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CA-01-33-AG-2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>160</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Garden: 64.12 sqm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>18619063</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CA-01-34-AG-3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>170</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Garden: 25.25 sqm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>18867589</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CA-01-36-B5-4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Club Park East Ap Update 2026</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>205</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>| Roof: 53 sqm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>17765964</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CV-01-03-00-1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>520</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Garden: 253.64 sqm | Roof: 68.27 sqm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>83608609</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CV-01-09-00-1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>520</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Garden: 484.21 sqm | Roof: 68.27 sqm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>84799701</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CV-02-03-00-1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>565</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>87973052</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LP-LV4P-02-00-01</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>280</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Garden: 226.45 sqm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>49808818</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LP-LV4P-07-00-01</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>280</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Garden: 262.01 sqm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>54213953</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LP-LV4P-27-00-01</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>280</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Garden: 261.19 sqm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>49168028</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LP-LV4P-28-00-01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>280</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Garden: 261.56 sqm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>50169621</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LP-LV4P-29-00-01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>280</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Garden: 261.19 sqm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>50792522</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LP-LV4P-30-00-01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>280</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Garden: 261.56 sqm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>53311995</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MV-03-40-LH-1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Phase-3</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>300</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Garden: 365.26 sqm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>80766761</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NP-IV-04-A5-03</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Feb 2026 (Value Offer)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>260</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>| Roof: 15 sqm</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>21553551</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>M-IV-A-221-B4-1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Phase-1M4</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>255</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>29325000</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>M-iV-B-252-A4-4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>245</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>28280596</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>M-iV-B-252-B2-3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>235</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>27025000</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>M-iV-B-252-B4-1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>245</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>28175000</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/availability/projects/mountain-view/mountain-view-icity-new-cairo.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-icity-new-cairo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for mountain-view-icity-new-cairo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -937,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1047,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1159,7 +1169,6 @@
       <c r="G2" t="n">
         <v>44.31</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1216,7 +1225,6 @@
       <c r="G3" t="n">
         <v>75.66</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1273,7 +1281,6 @@
       <c r="G4" t="n">
         <v>65.15000000000001</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1330,7 +1337,6 @@
       <c r="G5" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1387,7 +1393,6 @@
       <c r="G6" t="n">
         <v>87.42</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1444,7 +1449,6 @@
       <c r="G7" t="n">
         <v>88.76000000000001</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1501,7 +1505,6 @@
       <c r="G8" t="n">
         <v>36.76</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1558,7 +1561,6 @@
       <c r="G9" t="n">
         <v>64.12</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1615,7 +1617,6 @@
       <c r="G10" t="n">
         <v>25.25</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1672,7 +1673,6 @@
       <c r="G11" t="n">
         <v>253.64</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1729,7 +1729,6 @@
       <c r="G12" t="n">
         <v>484.21</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1786,7 +1785,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1843,7 +1841,6 @@
       <c r="G14" t="n">
         <v>261.56</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1854,7 +1851,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1900,7 +1897,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1911,7 +1907,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1957,7 +1953,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1968,7 +1963,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">

--- a/data/availability/projects/mountain-view/mountain-view-icity-new-cairo.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-icity-new-cairo.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
